--- a/AAII_Financials/Quarterly/JAMF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JAMF_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>JAMF</t>
   </si>
@@ -656,327 +656,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>150600</v>
+      </c>
+      <c r="E8" s="3">
         <v>142600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>135100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>132200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>130300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>124600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>115600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>108300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>103800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>95600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>86200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>80700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>76100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>70400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>62200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>60400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>57000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>54600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>48300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>44100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>41900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>39300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E9" s="3">
         <v>32200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>30900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>29700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>30400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>31200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>29400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>28200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>27200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>19300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13000</v>
-      </c>
-      <c r="W9" s="3">
-        <v>12600</v>
       </c>
       <c r="X9" s="3">
         <v>12600</v>
       </c>
       <c r="Y9" s="3">
+        <v>12600</v>
+      </c>
+      <c r="Z9" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>117500</v>
+      </c>
+      <c r="E10" s="3">
         <v>110400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>104200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>102500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>99900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>93400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>86200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>80100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>76600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>69100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>66900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>63400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>59000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>55200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>48600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>45400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>41600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>40500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>34800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>31100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>29300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>26700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,79 +1014,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E12" s="3">
         <v>33900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>34100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>31600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>29800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>30100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>33300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>24200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>16900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>9500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>8800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1144,79 +1160,85 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>2700</v>
+        <v>6800</v>
       </c>
       <c r="E14" s="3">
-        <v>700</v>
+        <v>4100</v>
       </c>
       <c r="F14" s="3">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="G14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H14" s="3">
         <v>1500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>10400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-2100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1600</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W14" s="3">
         <v>900</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1224,19 +1246,19 @@
         <v>8900</v>
       </c>
       <c r="E15" s="3">
-        <v>8800</v>
+        <v>8900</v>
       </c>
       <c r="F15" s="3">
         <v>8800</v>
       </c>
       <c r="G15" s="3">
+        <v>8800</v>
+      </c>
+      <c r="H15" s="3">
         <v>8600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>8300</v>
       </c>
       <c r="J15" s="3">
         <v>8300</v>
@@ -1245,40 +1267,40 @@
         <v>8300</v>
       </c>
       <c r="L15" s="3">
+        <v>8300</v>
+      </c>
+      <c r="M15" s="3">
         <v>8200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>6600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>6700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>7100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>6600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5500</v>
-      </c>
-      <c r="T15" s="3">
-        <v>5600</v>
       </c>
       <c r="U15" s="3">
         <v>5600</v>
       </c>
       <c r="V15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="W15" s="3">
         <v>6300</v>
-      </c>
-      <c r="W15" s="3">
-        <v>5400</v>
       </c>
       <c r="X15" s="3">
         <v>5400</v>
@@ -1286,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>5400</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>170900</v>
+      </c>
+      <c r="E17" s="3">
         <v>174500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>172700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>157700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>155000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>153200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>177500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>132000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>129900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>125900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>102300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>84900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>90900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>76000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>58000</v>
-      </c>
-      <c r="R17" s="3">
-        <v>66900</v>
       </c>
       <c r="S17" s="3">
         <v>66900</v>
       </c>
       <c r="T17" s="3">
+        <v>66900</v>
+      </c>
+      <c r="U17" s="3">
         <v>54400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>52700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>50300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>48600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>44300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-31900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-37600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-25500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-24700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-28600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-61900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-23700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-26100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-30300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-16100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-14800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,43 +1511,44 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-200</v>
       </c>
       <c r="O20" s="3">
         <v>-200</v>
@@ -1524,105 +1557,111 @@
         <v>-200</v>
       </c>
       <c r="Q20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-20100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-22700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-9400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-17300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-48600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-16900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>13700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="W21" s="3">
         <v>2600</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1641,41 +1680,41 @@
       <c r="H22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3">
         <v>600</v>
-      </c>
-      <c r="J22" s="3">
-        <v>900</v>
       </c>
       <c r="K22" s="3">
         <v>900</v>
       </c>
       <c r="L22" s="3">
+        <v>900</v>
+      </c>
+      <c r="M22" s="3">
         <v>1400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>100</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
       </c>
       <c r="P22" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>4700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>4800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>5500</v>
       </c>
       <c r="U22" s="3">
         <v>5500</v>
@@ -1684,158 +1723,167 @@
         <v>5500</v>
       </c>
       <c r="W22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="X22" s="3">
         <v>4300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-32800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-35100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-23600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-22500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-31200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-63200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-25400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-27000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-32000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-11500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-14800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-12900</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-3200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-3500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-3000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-32300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-36200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-24200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-21200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-63100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-23800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-16500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-32300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-36200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-24200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-21200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-31300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-63100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-23800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-30400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,43 +2397,46 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E32" s="3">
         <v>900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>200</v>
       </c>
       <c r="O32" s="3">
         <v>200</v>
@@ -2376,105 +2445,111 @@
         <v>200</v>
       </c>
       <c r="Q32" s="3">
+        <v>200</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-32300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-36200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-24200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-21200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-31300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-63100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-23800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-30400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-11200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-32300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-36200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-24200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-21200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-31300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-63100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-23800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-30400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-11200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,59 +2830,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>243600</v>
+      </c>
+      <c r="E41" s="3">
         <v>227600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>211500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>224300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>225500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>182300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>164600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>177200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>227100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>226500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>196200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>194900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>177500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>38400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22700</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>10</v>
       </c>
@@ -2816,8 +2902,11 @@
       <c r="Y41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,59 +2976,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>108200</v>
+      </c>
+      <c r="E43" s="3">
         <v>96000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>101000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>85200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>88600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>93300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>96900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>81400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>79800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>70100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>67200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>76500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>69700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>64800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>53800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>46700</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>10</v>
       </c>
@@ -2958,8 +3050,11 @@
       <c r="Y43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3029,59 +3124,62 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E45" s="3">
         <v>48400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>46600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>48200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>38100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>38900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>37900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>38100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>34700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>28500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>22700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>25900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>24500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>25000</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>10</v>
       </c>
@@ -3100,59 +3198,62 @@
       <c r="Y45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>402600</v>
+      </c>
+      <c r="E46" s="3">
         <v>372000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>359000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>333800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>351000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>357700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>317200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>284100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>291600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>331200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>321300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>301200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>287200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>268100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>116700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>94400</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>10</v>
       </c>
@@ -3171,8 +3272,11 @@
       <c r="Y46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3242,59 +3346,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E48" s="3">
         <v>36500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>38900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>43200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>43600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>44400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>46800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>38300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12300</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>10</v>
       </c>
@@ -3313,59 +3420,62 @@
       <c r="Y48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1075000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1073300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1068000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1072300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1075700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1015600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1057200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1093100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1110300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1122800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>730900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>739400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>744400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>749900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>758200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>766600</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>10</v>
       </c>
@@ -3384,8 +3494,11 @@
       <c r="Y49" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,59 +3642,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>79200</v>
+      </c>
+      <c r="E52" s="3">
         <v>70200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>67100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>62000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>59600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>50600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>47300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>42300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>40200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>58500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>54100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>57700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>27600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>26300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>22900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>20700</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>10</v>
       </c>
@@ -3597,8 +3716,11 @@
       <c r="Y52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,59 +3790,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1589700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1552100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1533000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1509000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1529500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1467400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1466100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1466300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1480400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1530100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1123500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1115200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1074300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1055300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>909400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>893900</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>10</v>
       </c>
@@ -3739,8 +3864,11 @@
       <c r="Y54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,59 +3922,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E57" s="3">
         <v>21100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>10</v>
       </c>
@@ -3864,8 +3994,11 @@
       <c r="Y57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3935,59 +4068,62 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>396200</v>
+      </c>
+      <c r="E59" s="3">
         <v>380200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>348400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>327900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>345600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>329800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>300300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>280300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>277200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>310400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>219400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>197200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>192600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>174300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>157500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>146300</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>10</v>
       </c>
@@ -4006,59 +4142,62 @@
       <c r="Y59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>422200</v>
+      </c>
+      <c r="E60" s="3">
         <v>401300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>363600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>342900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>361000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>346700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>309800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>289100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>286500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>323100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>228400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>202900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>199600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>181000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>161400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>148100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>10</v>
       </c>
@@ -4077,41 +4216,44 @@
       <c r="Y60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>367000</v>
+      </c>
+      <c r="E61" s="3">
         <v>366400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>365800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>365100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>364500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>363900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>363300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>362600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>362000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>361500</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4122,14 +4264,14 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>201900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>201600</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4148,59 +4290,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E62" s="3">
         <v>84900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>95300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>95500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>102700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>97100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>99000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>92600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>93400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>98800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>91100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>93000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>63700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>58900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>49200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>47800</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>10</v>
       </c>
@@ -4219,8 +4364,11 @@
       <c r="Y62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,59 +4586,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>872100</v>
+      </c>
+      <c r="E66" s="3">
         <v>852600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>824700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>803500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>828200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>807700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>772100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>744400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>742000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>783300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>319600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>295900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>263300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>239900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>412500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>397400</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4503,8 +4660,11 @@
       <c r="Y66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,59 +4984,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-418800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-401400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-369100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-332900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-308700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-287500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-256200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-193000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-167400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-143700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-113300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-90800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-92200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-78800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-73700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-73300</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>10</v>
       </c>
@@ -4885,8 +5058,11 @@
       <c r="Y72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,59 +5280,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>717500</v>
+      </c>
+      <c r="E76" s="3">
         <v>699400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>708400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>705500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>701300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>659800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>693900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>721900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>738400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>746800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>804000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>819300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>811000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>815400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>496800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>496500</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>10</v>
       </c>
@@ -5169,8 +5354,11 @@
       <c r="Y76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-32300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-36200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-24200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-21200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-31300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-63100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-23800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-30400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-11200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,59 +5611,60 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E83" s="3">
         <v>12800</v>
-      </c>
-      <c r="E83" s="3">
-        <v>12400</v>
       </c>
       <c r="F83" s="3">
         <v>12400</v>
       </c>
       <c r="G83" s="3">
+        <v>12400</v>
+      </c>
+      <c r="H83" s="3">
         <v>13100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>13900</v>
       </c>
       <c r="J83" s="3">
         <v>13900</v>
       </c>
       <c r="K83" s="3">
+        <v>13900</v>
+      </c>
+      <c r="L83" s="3">
         <v>13800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13700</v>
-      </c>
-      <c r="M83" s="3">
-        <v>9800</v>
       </c>
       <c r="N83" s="3">
         <v>9800</v>
       </c>
       <c r="O83" s="3">
+        <v>9800</v>
+      </c>
+      <c r="P83" s="3">
         <v>10100</v>
-      </c>
-      <c r="P83" s="3">
-        <v>9400</v>
       </c>
       <c r="Q83" s="3">
         <v>9400</v>
       </c>
       <c r="R83" s="3">
+        <v>9400</v>
+      </c>
+      <c r="S83" s="3">
         <v>9600</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>10</v>
       </c>
@@ -5485,8 +5683,11 @@
       <c r="Y83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,59 +6053,62 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E89" s="3">
         <v>33300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-24800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>27200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>46500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>19300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>26800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>34000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>19800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>23600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>18300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8800</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>10</v>
       </c>
@@ -5911,8 +6127,11 @@
       <c r="Y89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,59 +6157,60 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-700</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
         <v>-700</v>
       </c>
       <c r="F91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1000</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>10</v>
       </c>
@@ -6009,8 +6229,11 @@
       <c r="Y91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,59 +6377,62 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-351700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>10</v>
       </c>
@@ -6222,8 +6451,11 @@
       <c r="Y94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,59 +6775,62 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>2700</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>2500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-23400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>326800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>4000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>115900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>10</v>
       </c>
@@ -6604,47 +6849,50 @@
       <c r="Y100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-600</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-100</v>
       </c>
       <c r="K101" s="3">
         <v>-100</v>
       </c>
       <c r="L101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>10</v>
       </c>
@@ -6660,8 +6908,8 @@
       <c r="T101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -6675,59 +6923,62 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E102" s="3">
         <v>16100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-24100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>43100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>17800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-50600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>30300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>139000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9800</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>10</v>
       </c>
@@ -6744,6 +6995,9 @@
         <v>10</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JAMF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JAMF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
   <si>
     <t>JAMF</t>
   </si>
@@ -656,339 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>152100</v>
+      </c>
+      <c r="E8" s="3">
         <v>150600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>142600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>135100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>132200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>130300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>124600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>115600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>108300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>103800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>95600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>86200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>80700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>76100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>70400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>62200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>60400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>57000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>54600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>48300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>44100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>41900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>39300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E9" s="3">
         <v>33100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>32200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>30900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>29700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>30400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>31200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>29400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>28200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>27200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>17100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13000</v>
-      </c>
-      <c r="X9" s="3">
-        <v>12600</v>
       </c>
       <c r="Y9" s="3">
         <v>12600</v>
       </c>
       <c r="Z9" s="3">
+        <v>12600</v>
+      </c>
+      <c r="AA9" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>117100</v>
+      </c>
+      <c r="E10" s="3">
         <v>117500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>110400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>104200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>102500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>99900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>93400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>86200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>80100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>76600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>69100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>66900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>63400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>59000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>55200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>48600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>45400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>41600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>40500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>34800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>31100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>29300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>26700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,82 +1028,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E12" s="3">
         <v>32200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>33900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>34100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>31600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>29800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>30100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>33300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>23300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>16900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>11700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>8400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1163,105 +1180,111 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E14" s="3">
         <v>6800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>10400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-2100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1600</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X14" s="3">
         <v>900</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>8900</v>
+        <v>8300</v>
       </c>
       <c r="E15" s="3">
         <v>8900</v>
       </c>
       <c r="F15" s="3">
-        <v>8800</v>
+        <v>8900</v>
       </c>
       <c r="G15" s="3">
         <v>8800</v>
       </c>
       <c r="H15" s="3">
+        <v>8800</v>
+      </c>
+      <c r="I15" s="3">
         <v>8600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8400</v>
-      </c>
-      <c r="J15" s="3">
-        <v>8300</v>
       </c>
       <c r="K15" s="3">
         <v>8300</v>
@@ -1270,40 +1293,40 @@
         <v>8300</v>
       </c>
       <c r="M15" s="3">
+        <v>8300</v>
+      </c>
+      <c r="N15" s="3">
         <v>8200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>6600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>7100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>6500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>6600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5500</v>
-      </c>
-      <c r="U15" s="3">
-        <v>5600</v>
       </c>
       <c r="V15" s="3">
         <v>5600</v>
       </c>
       <c r="W15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="X15" s="3">
         <v>6300</v>
-      </c>
-      <c r="X15" s="3">
-        <v>5400</v>
       </c>
       <c r="Y15" s="3">
         <v>5400</v>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>5400</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>173200</v>
+      </c>
+      <c r="E17" s="3">
         <v>170900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>174500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>172700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>157700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>155000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>153200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>177500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>132000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>129900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>125900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>102300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>84900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>90900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>76000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>58000</v>
-      </c>
-      <c r="S17" s="3">
-        <v>66900</v>
       </c>
       <c r="T17" s="3">
         <v>66900</v>
       </c>
       <c r="U17" s="3">
+        <v>66900</v>
+      </c>
+      <c r="V17" s="3">
         <v>54400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>52700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>50300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>48600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>44300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-20300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-31900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-37600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-25500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-24700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-28600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-61900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-23700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-26100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-30300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-16100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,46 +1545,47 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E20" s="3">
         <v>4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-200</v>
       </c>
       <c r="P20" s="3">
         <v>-200</v>
@@ -1560,108 +1594,114 @@
         <v>-200</v>
       </c>
       <c r="R20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-20100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-22700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-17300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-48600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-12300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X21" s="3">
         <v>2600</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1683,41 +1723,41 @@
       <c r="I22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K22" s="3">
         <v>600</v>
-      </c>
-      <c r="K22" s="3">
-        <v>900</v>
       </c>
       <c r="L22" s="3">
         <v>900</v>
       </c>
       <c r="M22" s="3">
+        <v>900</v>
+      </c>
+      <c r="N22" s="3">
         <v>1400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>200</v>
-      </c>
-      <c r="O22" s="3">
-        <v>100</v>
       </c>
       <c r="P22" s="3">
         <v>100</v>
       </c>
       <c r="Q22" s="3">
+        <v>100</v>
+      </c>
+      <c r="R22" s="3">
         <v>1200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>4700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>5500</v>
       </c>
       <c r="V22" s="3">
         <v>5500</v>
@@ -1726,164 +1766,173 @@
         <v>5500</v>
       </c>
       <c r="X22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="Y22" s="3">
         <v>4300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-32800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-35100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-23600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-22500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-31200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-63200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-25400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-27000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-32000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-14800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-12900</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1900</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>-3200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-3500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-32300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-36200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-24200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-21200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-63100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-23800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-30400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-16500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-11200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-32300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-36200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-24200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-21200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-31300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-63100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-23800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-30400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-11200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,46 +2467,49 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>200</v>
       </c>
       <c r="P32" s="3">
         <v>200</v>
@@ -2448,108 +2518,114 @@
         <v>200</v>
       </c>
       <c r="R32" s="3">
+        <v>200</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-32300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-36200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-24200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-21200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-31300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-63100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-23800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-30400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-11200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-32300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-36200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-24200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-21200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-31300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-63100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-23800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-30400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-11200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,62 +2917,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>224500</v>
+      </c>
+      <c r="E41" s="3">
         <v>243600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>227600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>211500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>200300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>224300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>225500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>182300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>164600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>177200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>227100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>226500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>196200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>194900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>177500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>38400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>22700</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>10</v>
       </c>
@@ -2905,8 +2992,11 @@
       <c r="Z41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2979,62 +3069,65 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>95500</v>
+      </c>
+      <c r="E43" s="3">
         <v>108200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>96000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>101000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>85200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>88600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>93300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>96900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>81400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>79800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>70100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>67200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>76500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>69700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>64800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>53800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>46700</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>10</v>
       </c>
@@ -3053,8 +3146,11 @@
       <c r="Z43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3127,62 +3223,65 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E45" s="3">
         <v>50800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>48400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>46600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>48200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>38100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>38900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>37900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>38100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>34700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>33900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>28500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>22700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>25900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>24500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>25000</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>10</v>
       </c>
@@ -3201,62 +3300,65 @@
       <c r="Z45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>386700</v>
+      </c>
+      <c r="E46" s="3">
         <v>402600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>372000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>359000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>333800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>351000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>357700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>317200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>284100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>291600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>331200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>321300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>301200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>287200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>268100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>116700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>94400</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>10</v>
       </c>
@@ -3275,8 +3377,11 @@
       <c r="Z46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3349,62 +3454,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E48" s="3">
         <v>32800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>36500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>41000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>43200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>43600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>44400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>46800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>38300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12300</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>10</v>
       </c>
@@ -3423,62 +3531,65 @@
       <c r="Z48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1062300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1075000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1073300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1068000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1072300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1075700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1015600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1057200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1093100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1110300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1122800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>730900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>739400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>744400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>749900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>758200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>766600</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>10</v>
       </c>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,62 +3762,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>81900</v>
+      </c>
+      <c r="E52" s="3">
         <v>79200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>70200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>67100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>62000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>59600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>50600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>47300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>42300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>40200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>58500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>54100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>57700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>27600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>26300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>22900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>20700</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>10</v>
       </c>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,62 +3916,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1563800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1589700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1552100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1533000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1509000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1529500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1467400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1466100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1466300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1480400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1530100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1123500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1115200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1074300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1055300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>909400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>893900</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>10</v>
       </c>
@@ -3867,8 +3993,11 @@
       <c r="Z54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,62 +4053,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E57" s="3">
         <v>25900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>21100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1800</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>10</v>
       </c>
@@ -3997,8 +4128,11 @@
       <c r="Z57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4071,62 +4205,65 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>383600</v>
+      </c>
+      <c r="E59" s="3">
         <v>396200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>380200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>348400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>327900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>345600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>329800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>300300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>280300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>277200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>310400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>219400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>197200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>192600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>174300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>157500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>146300</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>10</v>
       </c>
@@ -4145,62 +4282,65 @@
       <c r="Z59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>404000</v>
+      </c>
+      <c r="E60" s="3">
         <v>422200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>401300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>363600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>342900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>361000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>346700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>309800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>289100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>286500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>323100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>228400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>202900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>199600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>181000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>161400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>148100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>10</v>
       </c>
@@ -4219,44 +4359,47 @@
       <c r="Z60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>367600</v>
+      </c>
+      <c r="E61" s="3">
         <v>367000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>366400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>365800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>365100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>364500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>363900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>363300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>362600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>362000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>361500</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -4267,14 +4410,14 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>201900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>201600</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4293,62 +4436,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E62" s="3">
         <v>83000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>84900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>95300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>95500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>102700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>97100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>99000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>92600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>93400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>98800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>91100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>93000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>63700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>58900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>49200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>47800</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>10</v>
       </c>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,62 +4744,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>847700</v>
+      </c>
+      <c r="E66" s="3">
         <v>872100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>852600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>824700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>803500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>828200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>807700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>772100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>744400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>742000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>783300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>319600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>295900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>263300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>239900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>412500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>397400</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4663,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,62 +5158,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-439300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-418800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-401400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-369100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-332900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-308700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-287500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-256200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-193000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-167400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-143700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-113300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-90800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-92200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-78800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-73700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-73300</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>10</v>
       </c>
@@ -5061,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,62 +5466,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>716100</v>
+      </c>
+      <c r="E76" s="3">
         <v>717500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>699400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>708400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>705500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>701300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>659800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>693900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>721900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>738400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>746800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>804000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>819300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>811000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>815400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>496800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>496500</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>10</v>
       </c>
@@ -5357,8 +5543,11 @@
       <c r="Z76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-32300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-36200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-24200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-21200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-31300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-63100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-23800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-30400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-11200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,62 +5810,63 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E83" s="3">
         <v>12700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12800</v>
-      </c>
-      <c r="F83" s="3">
-        <v>12400</v>
       </c>
       <c r="G83" s="3">
         <v>12400</v>
       </c>
       <c r="H83" s="3">
+        <v>12400</v>
+      </c>
+      <c r="I83" s="3">
         <v>13100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>13900</v>
       </c>
       <c r="K83" s="3">
         <v>13900</v>
       </c>
       <c r="L83" s="3">
+        <v>13900</v>
+      </c>
+      <c r="M83" s="3">
         <v>13800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>9800</v>
       </c>
       <c r="O83" s="3">
         <v>9800</v>
       </c>
       <c r="P83" s="3">
+        <v>9800</v>
+      </c>
+      <c r="Q83" s="3">
         <v>10100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>9400</v>
       </c>
       <c r="R83" s="3">
         <v>9400</v>
       </c>
       <c r="S83" s="3">
+        <v>9400</v>
+      </c>
+      <c r="T83" s="3">
         <v>9600</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>10</v>
       </c>
@@ -5686,8 +5885,11 @@
       <c r="Z83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,62 +6270,65 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E89" s="3">
         <v>15900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>33300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-24800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>27200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>46500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>19300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>26800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>34000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>23600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>18300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8800</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>10</v>
       </c>
@@ -6130,8 +6347,11 @@
       <c r="Z89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,62 +6378,63 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-700</v>
       </c>
       <c r="F91" s="3">
         <v>-700</v>
       </c>
       <c r="G91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1000</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>10</v>
       </c>
@@ -6232,8 +6453,11 @@
       <c r="Z91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,62 +6607,65 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-351700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>10</v>
       </c>
@@ -6454,8 +6684,11 @@
       <c r="Z94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,62 +7021,65 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2700</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>2500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-23400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>326800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>115900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>10</v>
       </c>
@@ -6852,50 +7098,53 @@
       <c r="Z100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-100</v>
       </c>
       <c r="L101" s="3">
         <v>-100</v>
       </c>
       <c r="M101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>10</v>
       </c>
@@ -6911,8 +7160,8 @@
       <c r="U101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -6926,62 +7175,65 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E102" s="3">
         <v>16000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>16100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-24100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>43100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>17800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-50600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>30300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>17500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>139000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-9800</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>10</v>
       </c>
@@ -6998,6 +7250,9 @@
         <v>10</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JAMF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JAMF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
   <si>
     <t>JAMF</t>
   </si>
@@ -656,352 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E8" s="3">
         <v>152100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>150600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>142600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>135100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>132200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>130300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>124600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>115600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>108300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>103800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>95600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>86200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>80700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>76100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>70400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>62200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>60400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>57000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>54600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>48300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>44100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>41900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>39300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E9" s="3">
         <v>35000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>33100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>32200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>30900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>29700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>31200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>29400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>28200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>27200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>17300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>14100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>13000</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>12600</v>
       </c>
       <c r="Z9" s="3">
         <v>12600</v>
       </c>
       <c r="AA9" s="3">
+        <v>12600</v>
+      </c>
+      <c r="AB9" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>118200</v>
+      </c>
+      <c r="E10" s="3">
         <v>117100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>117500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>110400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>104200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>102500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>99900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>93400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>86200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>80100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>76600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>69100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>66900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>63400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>59000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>55200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>48600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>45400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>41600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>40500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>34800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>31100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>29300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>26700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,85 +1042,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E12" s="3">
         <v>32900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>32200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>33900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>34100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>31600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>29800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>30100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>33300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>24200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>16900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>14900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>11700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>13400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>8800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>8400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1183,85 +1200,91 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E14" s="3">
         <v>11400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>10400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-2100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y14" s="3">
         <v>900</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1269,25 +1292,25 @@
         <v>8300</v>
       </c>
       <c r="E15" s="3">
-        <v>8900</v>
+        <v>8300</v>
       </c>
       <c r="F15" s="3">
         <v>8900</v>
       </c>
       <c r="G15" s="3">
-        <v>8800</v>
+        <v>8900</v>
       </c>
       <c r="H15" s="3">
         <v>8800</v>
       </c>
       <c r="I15" s="3">
+        <v>8800</v>
+      </c>
+      <c r="J15" s="3">
         <v>8600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>8300</v>
       </c>
       <c r="L15" s="3">
         <v>8300</v>
@@ -1296,40 +1319,40 @@
         <v>8300</v>
       </c>
       <c r="N15" s="3">
+        <v>8300</v>
+      </c>
+      <c r="O15" s="3">
         <v>8200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>7100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>6400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>6500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>6600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>5500</v>
-      </c>
-      <c r="V15" s="3">
-        <v>5600</v>
       </c>
       <c r="W15" s="3">
         <v>5600</v>
       </c>
       <c r="X15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Y15" s="3">
         <v>6300</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>5400</v>
       </c>
       <c r="Z15" s="3">
         <v>5400</v>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>5400</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E17" s="3">
         <v>173200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>170900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>174500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>172700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>157700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>155000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>153200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>177500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>132000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>129900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>125900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>102300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>84900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>90900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>76000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>58000</v>
-      </c>
-      <c r="T17" s="3">
-        <v>66900</v>
       </c>
       <c r="U17" s="3">
         <v>66900</v>
       </c>
       <c r="V17" s="3">
+        <v>66900</v>
+      </c>
+      <c r="W17" s="3">
         <v>54400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>52700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>50300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>48600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>44300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-21100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-20300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-31900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-37600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-25500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-24700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-28600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-61900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-23700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-26100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-30300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-16100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-14800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-6500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-4400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,49 +1579,50 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E20" s="3">
         <v>1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-200</v>
       </c>
       <c r="Q20" s="3">
         <v>-200</v>
@@ -1597,111 +1631,117 @@
         <v>-200</v>
       </c>
       <c r="S20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-20100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-22700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-11200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-48600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-12300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-16900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>13700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y21" s="3">
         <v>2600</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1726,41 +1766,41 @@
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="3">
         <v>600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>900</v>
       </c>
       <c r="M22" s="3">
         <v>900</v>
       </c>
       <c r="N22" s="3">
+        <v>900</v>
+      </c>
+      <c r="O22" s="3">
         <v>1400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>200</v>
-      </c>
-      <c r="P22" s="3">
-        <v>100</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
       </c>
       <c r="R22" s="3">
+        <v>100</v>
+      </c>
+      <c r="S22" s="3">
         <v>1200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>5500</v>
       </c>
       <c r="W22" s="3">
         <v>5500</v>
@@ -1769,170 +1809,179 @@
         <v>5500</v>
       </c>
       <c r="Y22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="Z22" s="3">
         <v>4300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>4700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-32800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-35100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-23600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-22500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-31200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-63200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-25400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-27000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-32000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-14800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-12900</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-4900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1900</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-3200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-3500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-20500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-32300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-36200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-24200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-21200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-31300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-63100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-23800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-30400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-16500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-11200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-20500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-32300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-36200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-24200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-21200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-31300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-63100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-23800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-30400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-16500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-11200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,49 +2537,52 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
-      </c>
-      <c r="P32" s="3">
-        <v>200</v>
       </c>
       <c r="Q32" s="3">
         <v>200</v>
@@ -2521,111 +2591,117 @@
         <v>200</v>
       </c>
       <c r="S32" s="3">
+        <v>200</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-20500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-32300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-36200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-24200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-21200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-31300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-63100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-23800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-30400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-16500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-11200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-20500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-32300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-36200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-24200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-21200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-31300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-63100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-23800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-30400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-16500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-11200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,65 +3004,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>200900</v>
+      </c>
+      <c r="E41" s="3">
         <v>224500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>243600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>227600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>211500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>200300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>224300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>225500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>182300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>164600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>177200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>227100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>226500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>196200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>194900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>177500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>38400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>22700</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>10</v>
       </c>
@@ -2995,8 +3082,11 @@
       <c r="AA41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3072,65 +3162,68 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>109100</v>
+      </c>
+      <c r="E43" s="3">
         <v>95500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>108200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>96000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>101000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>85200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>88600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>93300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>96900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>81400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>79800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>70100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>67200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>76500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>69700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>64800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>53800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>46700</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>10</v>
       </c>
@@ -3149,8 +3242,11 @@
       <c r="AA43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3226,65 +3322,68 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>64100</v>
+      </c>
+      <c r="E45" s="3">
         <v>66700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>50800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>48400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>46600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>48200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>38100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>38900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>37900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>34700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>22700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>25900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>24500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>25000</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>10</v>
       </c>
@@ -3303,65 +3402,68 @@
       <c r="AA45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E46" s="3">
         <v>386700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>402600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>372000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>359000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>333800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>351000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>357700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>317200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>284100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>291600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>331200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>321300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>301200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>287200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>268100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>116700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>94400</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>10</v>
       </c>
@@ -3380,8 +3482,11 @@
       <c r="AA46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3457,65 +3562,68 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E48" s="3">
         <v>32900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>36500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>41000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>43200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>43600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>44400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>46800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>38300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12300</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>10</v>
       </c>
@@ -3534,65 +3642,68 @@
       <c r="AA48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1053200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1062300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1075000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1073300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1068000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1072300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1075700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1015600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1057200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1093100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1110300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1122800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>730900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>739400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>744400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>749900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>758200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>766600</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>10</v>
       </c>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,65 +3882,68 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>87200</v>
+      </c>
+      <c r="E52" s="3">
         <v>81900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>79200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>70200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>67100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>62000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>59600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>50600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>47300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>42300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>40200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>58500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>54100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>57700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>27600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>26300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>22900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>20700</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>10</v>
       </c>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,65 +4042,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1546700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1563800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1589700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1552100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1533000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1509000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1529500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1467400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1466100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1466300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1480400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1530100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1123500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1115200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1074300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1055300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>909400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>893900</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>10</v>
       </c>
@@ -3996,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,65 +4184,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E57" s="3">
         <v>20400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>25900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>21100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1800</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>10</v>
       </c>
@@ -4131,8 +4262,11 @@
       <c r="AA57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4208,65 +4342,68 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>390100</v>
+      </c>
+      <c r="E59" s="3">
         <v>383600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>396200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>380200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>348400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>327900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>345600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>329800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>300300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>280300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>277200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>310400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>219400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>197200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>192600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>174300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>157500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>146300</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>10</v>
       </c>
@@ -4285,65 +4422,68 @@
       <c r="AA59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>409000</v>
+      </c>
+      <c r="E60" s="3">
         <v>404000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>422200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>401300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>363600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>342900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>361000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>346700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>309800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>289100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>286500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>323100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>228400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>202900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>199600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>181000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>161400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>148100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>10</v>
       </c>
@@ -4362,47 +4502,50 @@
       <c r="AA60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>368200</v>
+      </c>
+      <c r="E61" s="3">
         <v>367600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>367000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>366400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>365800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>365100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>364500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>363900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>363300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>362600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>362000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>361500</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4413,14 +4556,14 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>201900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>201600</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4439,65 +4582,68 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>77200</v>
+      </c>
+      <c r="E62" s="3">
         <v>76100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>83000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>84900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>95300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>95500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>102700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>97100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>99000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>92600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>93400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>98800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>91100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>93000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>63700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>58900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>49200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>47800</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>10</v>
       </c>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,65 +4902,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>854500</v>
+      </c>
+      <c r="E66" s="3">
         <v>847700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>872100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>852600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>824700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>803500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>828200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>807700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>772100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>744400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>742000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>783300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>319600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>295900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>263300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>239900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>412500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>397400</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4824,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,65 +5332,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-493900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-439300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-418800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-401400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-369100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-332900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-308700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-287500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-256200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-193000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-167400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-143700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-113300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-90800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-92200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-78800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-73700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-73300</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>10</v>
       </c>
@@ -5238,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,65 +5652,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>692300</v>
+      </c>
+      <c r="E76" s="3">
         <v>716100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>717500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>699400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>708400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>705500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>701300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>659800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>693900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>721900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>738400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>746800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>804000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>819300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>811000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>815400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>496800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>496500</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>10</v>
       </c>
@@ -5546,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-20500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-32300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-36200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-24200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-21200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-31300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-63100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-23800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-30400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-16500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-11200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,65 +6009,66 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E83" s="3">
         <v>12000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>12400</v>
       </c>
       <c r="H83" s="3">
         <v>12400</v>
       </c>
       <c r="I83" s="3">
+        <v>12400</v>
+      </c>
+      <c r="J83" s="3">
         <v>13100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>13900</v>
       </c>
       <c r="L83" s="3">
         <v>13900</v>
       </c>
       <c r="M83" s="3">
+        <v>13900</v>
+      </c>
+      <c r="N83" s="3">
         <v>13800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13700</v>
-      </c>
-      <c r="O83" s="3">
-        <v>9800</v>
       </c>
       <c r="P83" s="3">
         <v>9800</v>
       </c>
       <c r="Q83" s="3">
+        <v>9800</v>
+      </c>
+      <c r="R83" s="3">
         <v>10100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>9400</v>
       </c>
       <c r="S83" s="3">
         <v>9400</v>
       </c>
       <c r="T83" s="3">
+        <v>9400</v>
+      </c>
+      <c r="U83" s="3">
         <v>9600</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>10</v>
       </c>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,65 +6487,68 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-15900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>33300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-24800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>27200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>46500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>26800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>34000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>19800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>23600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>18300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8800</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>10</v>
       </c>
@@ -6350,8 +6567,11 @@
       <c r="AA89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,65 +6599,66 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-700</v>
       </c>
       <c r="G91" s="3">
         <v>-700</v>
       </c>
       <c r="H91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1000</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>10</v>
       </c>
@@ -6456,8 +6677,11 @@
       <c r="AA91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,65 +6837,68 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-21900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-351700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>10</v>
       </c>
@@ -6687,8 +6917,11 @@
       <c r="AA94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,65 +7267,68 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-39200</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2700</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>2500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-23400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>326800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>115900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>10</v>
       </c>
@@ -7101,53 +7347,56 @@
       <c r="AA100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-100</v>
       </c>
       <c r="M101" s="3">
         <v>-100</v>
       </c>
       <c r="N101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>10</v>
       </c>
@@ -7163,8 +7412,8 @@
       <c r="V101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -7178,65 +7427,68 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-27300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-19000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>16000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>16100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-24100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>43100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>17800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-50600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>30300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>17500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>139000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>15700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9800</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>10</v>
       </c>
@@ -7253,6 +7505,9 @@
         <v>10</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JAMF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JAMF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
   <si>
     <t>JAMF</t>
   </si>
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>159300</v>
+      </c>
+      <c r="E8" s="3">
         <v>153000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>152100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>150600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>142600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>135100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>132200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>130300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>124600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>115600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>108300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>103800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>95600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>86200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>80700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>76100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>70400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>62200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>60400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>57000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>54600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>48300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>44100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>41900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>39300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>34800</v>
+        <v>32800</v>
       </c>
       <c r="E9" s="3">
-        <v>35000</v>
+        <v>31600</v>
       </c>
       <c r="F9" s="3">
-        <v>33100</v>
+        <v>31500</v>
       </c>
       <c r="G9" s="3">
-        <v>32200</v>
+        <v>29600</v>
       </c>
       <c r="H9" s="3">
-        <v>30900</v>
+        <v>28600</v>
       </c>
       <c r="I9" s="3">
-        <v>29700</v>
+        <v>27500</v>
       </c>
       <c r="J9" s="3">
+        <v>26400</v>
+      </c>
+      <c r="K9" s="3">
         <v>30400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>31200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>29400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>28200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>27200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>17100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>15400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>14100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>13500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13000</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>12600</v>
       </c>
       <c r="AA9" s="3">
         <v>12600</v>
       </c>
       <c r="AB9" s="3">
+        <v>12600</v>
+      </c>
+      <c r="AC9" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>118200</v>
+        <v>126400</v>
       </c>
       <c r="E10" s="3">
-        <v>117100</v>
+        <v>121400</v>
       </c>
       <c r="F10" s="3">
-        <v>117500</v>
+        <v>120600</v>
       </c>
       <c r="G10" s="3">
-        <v>110400</v>
+        <v>121100</v>
       </c>
       <c r="H10" s="3">
-        <v>104200</v>
+        <v>114000</v>
       </c>
       <c r="I10" s="3">
-        <v>102500</v>
+        <v>107600</v>
       </c>
       <c r="J10" s="3">
+        <v>105800</v>
+      </c>
+      <c r="K10" s="3">
         <v>99900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>93400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>86200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>80100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>76600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>69100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>66900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>63400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>59000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>55200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>48600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>45400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>41600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>40500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>34800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>31100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>29300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>26700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,88 +1056,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>34100</v>
+        <v>35700</v>
       </c>
       <c r="E12" s="3">
-        <v>32900</v>
+        <v>34500</v>
       </c>
       <c r="F12" s="3">
-        <v>32200</v>
+        <v>33000</v>
       </c>
       <c r="G12" s="3">
-        <v>33900</v>
+        <v>32500</v>
       </c>
       <c r="H12" s="3">
-        <v>34100</v>
+        <v>34200</v>
       </c>
       <c r="I12" s="3">
-        <v>31600</v>
+        <v>34400</v>
       </c>
       <c r="J12" s="3">
+        <v>32000</v>
+      </c>
+      <c r="K12" s="3">
         <v>29800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>30100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>33300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>24200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>23300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>14900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>11700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>9500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>8800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>8400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>7900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1203,117 +1220,123 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>5700</v>
+        <v>1200</v>
       </c>
       <c r="E14" s="3">
-        <v>11400</v>
+        <v>3400</v>
       </c>
       <c r="F14" s="3">
-        <v>6800</v>
+        <v>9300</v>
       </c>
       <c r="G14" s="3">
-        <v>4100</v>
+        <v>6200</v>
       </c>
       <c r="H14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I14" s="3">
+        <v>700</v>
+      </c>
+      <c r="J14" s="3">
+        <v>800</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="M14" s="3">
+        <v>600</v>
+      </c>
+      <c r="N14" s="3">
         <v>1200</v>
       </c>
-      <c r="J14" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K14" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>600</v>
-      </c>
-      <c r="M14" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>10400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>6900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-2100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z14" s="3">
         <v>900</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>8300</v>
+        <v>10000</v>
       </c>
       <c r="E15" s="3">
-        <v>8300</v>
+        <v>10100</v>
       </c>
       <c r="F15" s="3">
-        <v>8900</v>
+        <v>10200</v>
       </c>
       <c r="G15" s="3">
-        <v>8900</v>
+        <v>10900</v>
       </c>
       <c r="H15" s="3">
-        <v>8800</v>
+        <v>10900</v>
       </c>
       <c r="I15" s="3">
-        <v>8800</v>
+        <v>10600</v>
       </c>
       <c r="J15" s="3">
+        <v>10500</v>
+      </c>
+      <c r="K15" s="3">
         <v>8600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8400</v>
-      </c>
-      <c r="L15" s="3">
-        <v>8300</v>
       </c>
       <c r="M15" s="3">
         <v>8300</v>
@@ -1322,40 +1345,40 @@
         <v>8300</v>
       </c>
       <c r="O15" s="3">
+        <v>8300</v>
+      </c>
+      <c r="P15" s="3">
         <v>8200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>6400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>6500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>6600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>5500</v>
-      </c>
-      <c r="W15" s="3">
-        <v>5600</v>
       </c>
       <c r="X15" s="3">
         <v>5600</v>
       </c>
       <c r="Y15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Z15" s="3">
         <v>6300</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>5400</v>
       </c>
       <c r="AA15" s="3">
         <v>5400</v>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>5400</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>173000</v>
+        <v>174000</v>
       </c>
       <c r="E17" s="3">
-        <v>173200</v>
+        <v>169600</v>
       </c>
       <c r="F17" s="3">
-        <v>170900</v>
+        <v>163900</v>
       </c>
       <c r="G17" s="3">
-        <v>174500</v>
+        <v>164700</v>
       </c>
       <c r="H17" s="3">
-        <v>172700</v>
+        <v>171600</v>
       </c>
       <c r="I17" s="3">
-        <v>157700</v>
+        <v>172000</v>
       </c>
       <c r="J17" s="3">
+        <v>156900</v>
+      </c>
+      <c r="K17" s="3">
         <v>155000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>153200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>177500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>132000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>129900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>125900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>102300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>84900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>90900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>76000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>58000</v>
-      </c>
-      <c r="U17" s="3">
-        <v>66900</v>
       </c>
       <c r="V17" s="3">
         <v>66900</v>
       </c>
       <c r="W17" s="3">
+        <v>66900</v>
+      </c>
+      <c r="X17" s="3">
         <v>54400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>52700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>50300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>48600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>44300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-20000</v>
+        <v>-14700</v>
       </c>
       <c r="E18" s="3">
-        <v>-21100</v>
+        <v>-16500</v>
       </c>
       <c r="F18" s="3">
-        <v>-20300</v>
+        <v>-11800</v>
       </c>
       <c r="G18" s="3">
-        <v>-31900</v>
+        <v>-14000</v>
       </c>
       <c r="H18" s="3">
-        <v>-37600</v>
+        <v>-28900</v>
       </c>
       <c r="I18" s="3">
-        <v>-25500</v>
+        <v>-36900</v>
       </c>
       <c r="J18" s="3">
         <v>-24700</v>
       </c>
       <c r="K18" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="L18" s="3">
         <v>-28600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-61900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-23700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-26100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-30300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-6200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,52 +1613,53 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2100</v>
+        <v>-3400</v>
       </c>
       <c r="E20" s="3">
-        <v>1700</v>
+        <v>-400</v>
       </c>
       <c r="F20" s="3">
-        <v>4000</v>
+        <v>400</v>
       </c>
       <c r="G20" s="3">
-        <v>-900</v>
+        <v>-1900</v>
       </c>
       <c r="H20" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="I20" s="3">
-        <v>1900</v>
+        <v>-1000</v>
       </c>
       <c r="J20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K20" s="3">
         <v>2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-200</v>
       </c>
       <c r="R20" s="3">
         <v>-200</v>
@@ -1634,114 +1668,120 @@
         <v>-200</v>
       </c>
       <c r="T20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6000</v>
       </c>
-      <c r="E21" s="3">
-        <v>-7500</v>
-      </c>
       <c r="F21" s="3">
-        <v>-3600</v>
+        <v>-2000</v>
       </c>
       <c r="G21" s="3">
-        <v>-20100</v>
+        <v>-1200</v>
       </c>
       <c r="H21" s="3">
-        <v>-22700</v>
+        <v>-20700</v>
       </c>
       <c r="I21" s="3">
-        <v>-11200</v>
+        <v>-25300</v>
       </c>
       <c r="J21" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="K21" s="3">
         <v>-9400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-48600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-10600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-16900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>13700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2900</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z21" s="3">
         <v>2600</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1754,8 +1794,8 @@
       <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="G22" s="3">
+        <v>3600</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>10</v>
@@ -1769,41 +1809,41 @@
       <c r="K22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M22" s="3">
         <v>600</v>
-      </c>
-      <c r="M22" s="3">
-        <v>900</v>
       </c>
       <c r="N22" s="3">
         <v>900</v>
       </c>
       <c r="O22" s="3">
+        <v>900</v>
+      </c>
+      <c r="P22" s="3">
         <v>1400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>200</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>100</v>
       </c>
       <c r="R22" s="3">
         <v>100</v>
       </c>
       <c r="S22" s="3">
+        <v>100</v>
+      </c>
+      <c r="T22" s="3">
         <v>1200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>5500</v>
       </c>
       <c r="X22" s="3">
         <v>5500</v>
@@ -1812,176 +1852,185 @@
         <v>5500</v>
       </c>
       <c r="Z22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AA22" s="3">
         <v>4300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>4700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-32800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-35100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-23600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-22500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-31200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-63200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-25400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-27000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-32000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-15100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-14800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-12900</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E24" s="3">
         <v>1400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-4900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1900</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>-3200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-3500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-20500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-32300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-36200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-24200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-21200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-63100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-23800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-30400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-20500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-32300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-36200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-24200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-21200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-63100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-25600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-23800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-30400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-11200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,52 +2607,55 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2100</v>
+        <v>3400</v>
       </c>
       <c r="E32" s="3">
-        <v>-1700</v>
+        <v>400</v>
       </c>
       <c r="F32" s="3">
-        <v>-4000</v>
+        <v>-400</v>
       </c>
       <c r="G32" s="3">
-        <v>900</v>
+        <v>1900</v>
       </c>
       <c r="H32" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="I32" s="3">
-        <v>-1900</v>
+        <v>1000</v>
       </c>
       <c r="J32" s="3">
+        <v>600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>200</v>
       </c>
       <c r="R32" s="3">
         <v>200</v>
@@ -2594,114 +2664,120 @@
         <v>200</v>
       </c>
       <c r="T32" s="3">
+        <v>200</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-20500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-32300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-36200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-24200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-21200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-63100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-25600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-23800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-30400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-11200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-20500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-32300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-36200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-24200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-21200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-63100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-25600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-23800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-30400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-11200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,68 +3091,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>218400</v>
+      </c>
+      <c r="E41" s="3">
         <v>200900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>224500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>243600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>227600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>211500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>200300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>224300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>225500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>182300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>164600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>177200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>227100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>226500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>196200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>194900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>177500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>38400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>22700</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>10</v>
       </c>
@@ -3085,8 +3172,11 @@
       <c r="AB41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3165,68 +3255,71 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E43" s="3">
         <v>109100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>95500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>108200</v>
       </c>
-      <c r="G43" s="3">
-        <v>96000</v>
-      </c>
       <c r="H43" s="3">
+        <v>92400</v>
+      </c>
+      <c r="I43" s="3">
         <v>101000</v>
       </c>
-      <c r="I43" s="3">
-        <v>85200</v>
-      </c>
       <c r="J43" s="3">
+        <v>85800</v>
+      </c>
+      <c r="K43" s="3">
         <v>88600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>93300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>96900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>81400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>79800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>70100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>67200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>76500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>69700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>64800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>53800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>46700</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>10</v>
       </c>
@@ -3245,31 +3338,34 @@
       <c r="AB43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3325,68 +3421,71 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>64100</v>
+        <v>43800</v>
       </c>
       <c r="E45" s="3">
-        <v>66700</v>
+        <v>41900</v>
       </c>
       <c r="F45" s="3">
-        <v>50800</v>
+        <v>38200</v>
       </c>
       <c r="G45" s="3">
-        <v>48400</v>
+        <v>32900</v>
       </c>
       <c r="H45" s="3">
-        <v>46600</v>
+        <v>28800</v>
       </c>
       <c r="I45" s="3">
-        <v>48200</v>
+        <v>28400</v>
       </c>
       <c r="J45" s="3">
+        <v>24400</v>
+      </c>
+      <c r="K45" s="3">
         <v>38100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>38900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>37900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>34700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>33900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>27600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>28500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>22700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>25900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>24500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>25000</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>10</v>
       </c>
@@ -3405,68 +3504,71 @@
       <c r="AB45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>398700</v>
+      </c>
+      <c r="E46" s="3">
         <v>374000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>386700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>402600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>372000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>359000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>333800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>351000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>357700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>317200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>284100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>291600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>331200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>321300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>301200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>287200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>268100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>116700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>94400</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>10</v>
       </c>
@@ -3485,31 +3587,34 @@
       <c r="AB46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
+        <v>2000</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3565,68 +3670,71 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E48" s="3">
         <v>32300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>38900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>41000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>43200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>43600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>44400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>46800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>38300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12300</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>10</v>
       </c>
@@ -3645,68 +3753,71 @@
       <c r="AB48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1060600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1053200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1062300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1075000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1073300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1068000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1072300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1075700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1015600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1057200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1093100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1110300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1122800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>730900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>739400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>744400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>749900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>758200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>766600</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>10</v>
       </c>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,68 +4002,71 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>87200</v>
+        <v>23200</v>
       </c>
       <c r="E52" s="3">
-        <v>81900</v>
+        <v>11200</v>
       </c>
       <c r="F52" s="3">
-        <v>79200</v>
+        <v>27800</v>
       </c>
       <c r="G52" s="3">
-        <v>70200</v>
+        <v>11500</v>
       </c>
       <c r="H52" s="3">
-        <v>67100</v>
+        <v>21300</v>
       </c>
       <c r="I52" s="3">
-        <v>62000</v>
+        <v>20400</v>
       </c>
       <c r="J52" s="3">
+        <v>17500</v>
+      </c>
+      <c r="K52" s="3">
         <v>59600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>50600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>47300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>42300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>40200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>58500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>54100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>57700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>27600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>26300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>22900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>20700</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>10</v>
       </c>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,68 +4168,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1584200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1546700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1563800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1589700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1552100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1533000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1509000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1529500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1467400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1466100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1466300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1480400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1530100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1123500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1115200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1074300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1055300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>909400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>893900</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>10</v>
       </c>
@@ -4125,8 +4251,11 @@
       <c r="AB54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,68 +4315,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E57" s="3">
         <v>18900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>25900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1800</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>10</v>
       </c>
@@ -4265,31 +4396,34 @@
       <c r="AB57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>6200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4345,68 +4479,71 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>390100</v>
+        <v>329400</v>
       </c>
       <c r="E59" s="3">
-        <v>383600</v>
+        <v>317600</v>
       </c>
       <c r="F59" s="3">
-        <v>396200</v>
+        <v>313900</v>
       </c>
       <c r="G59" s="3">
-        <v>380200</v>
+        <v>320300</v>
       </c>
       <c r="H59" s="3">
-        <v>348400</v>
+        <v>312200</v>
       </c>
       <c r="I59" s="3">
-        <v>327900</v>
+        <v>292900</v>
       </c>
       <c r="J59" s="3">
+        <v>280500</v>
+      </c>
+      <c r="K59" s="3">
         <v>345600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>329800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>300300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>280300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>277200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>310400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>219400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>197200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>192600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>174300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>157500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>146300</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>10</v>
       </c>
@@ -4425,68 +4562,71 @@
       <c r="AB59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>419000</v>
+      </c>
+      <c r="E60" s="3">
         <v>409000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>404000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>422200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>401300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>363600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>342900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>361000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>346700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>309800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>289100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>286500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>323100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>228400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>202900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>199600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>181000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>161400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>148100</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>10</v>
       </c>
@@ -4505,50 +4645,53 @@
       <c r="AB60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>368200</v>
+        <v>386900</v>
       </c>
       <c r="E61" s="3">
-        <v>367600</v>
+        <v>384500</v>
       </c>
       <c r="F61" s="3">
-        <v>367000</v>
+        <v>384100</v>
       </c>
       <c r="G61" s="3">
-        <v>366400</v>
+        <v>383300</v>
       </c>
       <c r="H61" s="3">
-        <v>365800</v>
+        <v>383500</v>
       </c>
       <c r="I61" s="3">
-        <v>365100</v>
+        <v>384300</v>
       </c>
       <c r="J61" s="3">
+        <v>385400</v>
+      </c>
+      <c r="K61" s="3">
         <v>364500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>363900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>363300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>362600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>362000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>361500</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4559,14 +4702,14 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>201900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>201600</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4585,68 +4728,71 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>77200</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
-        <v>76100</v>
+        <v>700</v>
       </c>
       <c r="F62" s="3">
-        <v>83000</v>
+        <v>1300</v>
       </c>
       <c r="G62" s="3">
-        <v>84900</v>
+        <v>4800</v>
       </c>
       <c r="H62" s="3">
-        <v>95300</v>
+        <v>3600</v>
       </c>
       <c r="I62" s="3">
-        <v>95500</v>
+        <v>7200</v>
       </c>
       <c r="J62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="K62" s="3">
         <v>102700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>97100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>99000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>92600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>93400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>98800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>91100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>93000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>63700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>58900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>49200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>47800</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>10</v>
       </c>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,68 +5060,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>863700</v>
+      </c>
+      <c r="E66" s="3">
         <v>854500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>847700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>872100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>852600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>824700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>803500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>828200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>807700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>772100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>744400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>742000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>783300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>319600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>295900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>263300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>239900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>412500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>397400</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>10</v>
       </c>
@@ -4985,8 +5143,11 @@
       <c r="AB66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,68 +5506,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-506200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-493900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-439300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-418800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-401400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-369100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-332900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-308700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-287500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-256200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-193000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-167400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-143700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-113300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-90800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-92200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-78800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-73700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-73300</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>10</v>
       </c>
@@ -5415,8 +5589,11 @@
       <c r="AB72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,68 +5838,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>720500</v>
+      </c>
+      <c r="E76" s="3">
         <v>692300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>716100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>717500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>699400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>708400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>705500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>701300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>659800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>693900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>721900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>738400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>746800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>804000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>819300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>811000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>815400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>496800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>496500</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>10</v>
       </c>
@@ -5735,8 +5921,11 @@
       <c r="AB76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-20500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-32300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-36200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-24200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-21200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-63100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-25600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-23800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-30400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-11200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,68 +6208,69 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11900</v>
+        <v>1900</v>
       </c>
       <c r="E83" s="3">
-        <v>12000</v>
+        <v>1900</v>
       </c>
       <c r="F83" s="3">
-        <v>12700</v>
+        <v>1900</v>
       </c>
       <c r="G83" s="3">
-        <v>12800</v>
+        <v>1800</v>
       </c>
       <c r="H83" s="3">
-        <v>12400</v>
+        <v>1600</v>
       </c>
       <c r="I83" s="3">
-        <v>12400</v>
+        <v>1600</v>
       </c>
       <c r="J83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K83" s="3">
         <v>13100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>13900</v>
       </c>
       <c r="M83" s="3">
         <v>13900</v>
       </c>
       <c r="N83" s="3">
+        <v>13900</v>
+      </c>
+      <c r="O83" s="3">
         <v>13800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13700</v>
-      </c>
-      <c r="P83" s="3">
-        <v>9800</v>
       </c>
       <c r="Q83" s="3">
         <v>9800</v>
       </c>
       <c r="R83" s="3">
+        <v>9800</v>
+      </c>
+      <c r="S83" s="3">
         <v>10100</v>
-      </c>
-      <c r="S83" s="3">
-        <v>9400</v>
       </c>
       <c r="T83" s="3">
         <v>9400</v>
       </c>
       <c r="U83" s="3">
+        <v>9400</v>
+      </c>
+      <c r="V83" s="3">
         <v>9600</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>10</v>
       </c>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,68 +6704,71 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E89" s="3">
         <v>14300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-15900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>33300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>11600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-24800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>27200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>46500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>19300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>26800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>34000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>19800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>23600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>18300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8800</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>10</v>
       </c>
@@ -6570,8 +6787,11 @@
       <c r="AB89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,68 +6820,69 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-700</v>
       </c>
       <c r="H91" s="3">
         <v>-700</v>
       </c>
       <c r="I91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1000</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>10</v>
       </c>
@@ -6680,8 +6901,11 @@
       <c r="AB91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,68 +7067,71 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-21900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-27500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-351700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1000</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>10</v>
       </c>
@@ -6920,8 +7150,11 @@
       <c r="AB94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,31 +7183,32 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,68 +7513,71 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-39200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2700</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>2500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-23400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>326800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>115900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>10</v>
       </c>
@@ -7350,56 +7596,59 @@
       <c r="AB100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E101" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="F101" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3">
-        <v>-300</v>
+        <v>600</v>
       </c>
       <c r="H101" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="J101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-100</v>
       </c>
       <c r="N101" s="3">
         <v>-100</v>
       </c>
       <c r="O101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>10</v>
       </c>
@@ -7415,8 +7664,8 @@
       <c r="W101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -7430,68 +7679,71 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-27300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-19000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>16000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>16100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-24100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>43100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>17800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-50600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>30300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>17500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>139000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9800</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>10</v>
       </c>
@@ -7508,6 +7760,9 @@
         <v>10</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JAMF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JAMF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
   <si>
     <t>JAMF</t>
   </si>
@@ -656,378 +656,390 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E8" s="3">
         <v>159300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>153000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>152100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>150600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>142600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>135100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>132200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>130300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>124600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>115600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>108300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>103800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>95600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>86200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>80700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>76100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>70400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>62200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>60400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>57000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>54600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>48300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>44100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>41900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>39300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E9" s="3">
         <v>32800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>31600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>31500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>29600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>28600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>27500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>30400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>31200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>29400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>28200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>27200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>17300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>17100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>15000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>15400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>13500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13000</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>12600</v>
       </c>
       <c r="AB9" s="3">
         <v>12600</v>
       </c>
       <c r="AC9" s="3">
+        <v>12600</v>
+      </c>
+      <c r="AD9" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>130800</v>
+      </c>
+      <c r="E10" s="3">
         <v>126400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>121400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>120600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>121100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>114000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>107600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>105800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>99900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>93400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>86200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>80100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>76600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>69100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>66900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>63400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>59000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>55200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>48600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>45400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>41600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>40500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>34800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>31100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>29300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>26700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,91 +1069,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E12" s="3">
         <v>35700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>34500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>33000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>32500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>34200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>34400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>32000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>30100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>33300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>24200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>23300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>16900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>15300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>14900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>11700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>13400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>9500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>8800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>8400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,123 +1239,129 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>900</v>
+      </c>
+      <c r="E14" s="3">
         <v>1200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>9300</v>
       </c>
-      <c r="G14" s="3">
-        <v>6200</v>
-      </c>
       <c r="H14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I14" s="3">
         <v>2900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>10400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>6900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-2100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1600</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA14" s="3">
         <v>900</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E15" s="3">
         <v>10000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10200</v>
-      </c>
-      <c r="G15" s="3">
-        <v>10900</v>
       </c>
       <c r="H15" s="3">
         <v>10900</v>
       </c>
       <c r="I15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="J15" s="3">
         <v>10600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>10500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8400</v>
-      </c>
-      <c r="M15" s="3">
-        <v>8300</v>
       </c>
       <c r="N15" s="3">
         <v>8300</v>
@@ -1348,40 +1370,40 @@
         <v>8300</v>
       </c>
       <c r="P15" s="3">
+        <v>8300</v>
+      </c>
+      <c r="Q15" s="3">
         <v>8200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>6700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>7100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>6400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>6500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>6600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>5500</v>
-      </c>
-      <c r="X15" s="3">
-        <v>5600</v>
       </c>
       <c r="Y15" s="3">
         <v>5600</v>
       </c>
       <c r="Z15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AA15" s="3">
         <v>6300</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>5400</v>
       </c>
       <c r="AB15" s="3">
         <v>5400</v>
@@ -1389,8 +1411,11 @@
       <c r="AC15" s="3">
         <v>5400</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>174300</v>
+      </c>
+      <c r="E17" s="3">
         <v>174000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>169600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>163900</v>
       </c>
-      <c r="G17" s="3">
-        <v>164700</v>
-      </c>
       <c r="H17" s="3">
+        <v>164900</v>
+      </c>
+      <c r="I17" s="3">
         <v>171600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>172000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>156900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>155000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>153200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>177500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>132000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>129900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>125900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>102300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>84900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>90900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>76000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>58000</v>
-      </c>
-      <c r="V17" s="3">
-        <v>66900</v>
       </c>
       <c r="W17" s="3">
         <v>66900</v>
       </c>
       <c r="X17" s="3">
+        <v>66900</v>
+      </c>
+      <c r="Y17" s="3">
         <v>54400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>52700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>50300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>48600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>44300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-14700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-11800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-14000</v>
-      </c>
       <c r="H18" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-28900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-36900</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-24700</v>
       </c>
       <c r="K18" s="3">
         <v>-24700</v>
       </c>
       <c r="L18" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="M18" s="3">
         <v>-28600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-61900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-23700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-26100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-30300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-16100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-14800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-9900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-6200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,55 +1646,56 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-200</v>
       </c>
       <c r="S20" s="3">
         <v>-200</v>
@@ -1671,122 +1704,128 @@
         <v>-200</v>
       </c>
       <c r="U20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1200</v>
-      </c>
       <c r="H21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="I21" s="3">
         <v>-20700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-25300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-13600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-9400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-48600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-12300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-16900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>13700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2900</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA21" s="3">
         <v>2600</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AC21" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>10</v>
+      <c r="D22" s="3">
+        <v>3800</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>10</v>
@@ -1794,12 +1833,12 @@
       <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="3">
         <v>3600</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>10</v>
       </c>
@@ -1812,41 +1851,41 @@
       <c r="L22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N22" s="3">
         <v>600</v>
-      </c>
-      <c r="N22" s="3">
-        <v>900</v>
       </c>
       <c r="O22" s="3">
         <v>900</v>
       </c>
       <c r="P22" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>200</v>
-      </c>
-      <c r="R22" s="3">
-        <v>100</v>
       </c>
       <c r="S22" s="3">
         <v>100</v>
       </c>
       <c r="T22" s="3">
+        <v>100</v>
+      </c>
+      <c r="U22" s="3">
         <v>1200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>5500</v>
       </c>
       <c r="Y22" s="3">
         <v>5500</v>
@@ -1855,182 +1894,191 @@
         <v>5500</v>
       </c>
       <c r="AA22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AB22" s="3">
         <v>4300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>4700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-16300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-32800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-35100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-23600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-22500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-31200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-63200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-25400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-27000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-15100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-14800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-9800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-12900</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-4900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1900</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-3200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-3500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-20500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-32300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-36200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-24200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-21200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-63100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-23800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-16500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-20500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-32300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-36200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-24200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-21200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-63100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-23800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-16500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-11200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2504,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,55 +2676,58 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E32" s="3">
         <v>3400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
-      </c>
-      <c r="R32" s="3">
-        <v>200</v>
       </c>
       <c r="S32" s="3">
         <v>200</v>
@@ -2667,117 +2736,123 @@
         <v>200</v>
       </c>
       <c r="U32" s="3">
+        <v>200</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-20500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-32300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-36200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-24200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-21200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-63100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-23800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-11200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-20500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-32300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-36200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-24200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-21200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-63100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-23800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-11200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,71 +3177,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>224700</v>
+      </c>
+      <c r="E41" s="3">
         <v>218400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>200900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>224500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>243600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>227600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>211500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>200300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>224300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>225500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>182300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>164600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>177200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>227100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>226500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>196200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>194900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>177500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>38400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>22700</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>10</v>
       </c>
@@ -3175,8 +3261,11 @@
       <c r="AC41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,71 +3347,74 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>138800</v>
+      </c>
+      <c r="E43" s="3">
         <v>114000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>109100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>95500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>108200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>92400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>101000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>85800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>88600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>93300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>96900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>81400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>79800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>70100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>67200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>76500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>69700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>64800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>53800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>46700</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>10</v>
       </c>
@@ -3341,8 +3433,11 @@
       <c r="AC43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3367,8 +3462,8 @@
       <c r="J44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3424,71 +3519,74 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>44800</v>
+      </c>
+      <c r="E45" s="3">
         <v>43800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>41900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>38200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>32900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>28400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>24400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>38100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>37900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>38100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>34700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>33900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>27600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>28500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>22700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>25900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>24500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>25000</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>10</v>
       </c>
@@ -3507,71 +3605,74 @@
       <c r="AC45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>424700</v>
+      </c>
+      <c r="E46" s="3">
         <v>398700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>374000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>386700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>402600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>372000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>359000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>333800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>351000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>357700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>317200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>284100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>291600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>331200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>321300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>301200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>287200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>268100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>116700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>94400</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>10</v>
       </c>
@@ -3590,8 +3691,11 @@
       <c r="AC46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3604,21 +3708,21 @@
       <c r="F47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K47" s="3">
         <v>2000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J47" s="3">
-        <v>2000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -3673,71 +3777,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E48" s="3">
         <v>36900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>36500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>38900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>41000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>43200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>43600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>46800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>38300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12300</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>10</v>
       </c>
@@ -3756,71 +3863,74 @@
       <c r="AC48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1030400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1060600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1053200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1062300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1075000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1073300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1068000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1072300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1075700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1015600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1057200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1093100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1110300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1122800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>730900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>739400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>744400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>749900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>758200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>766600</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>10</v>
       </c>
@@ -3839,8 +3949,11 @@
       <c r="AC49" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,71 +4121,74 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E52" s="3">
         <v>23200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27800</v>
       </c>
-      <c r="G52" s="3">
-        <v>11500</v>
-      </c>
       <c r="H52" s="3">
+        <v>24400</v>
+      </c>
+      <c r="I52" s="3">
         <v>21300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>17500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>59600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>50600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>47300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>42300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>40200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>58500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>54100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>57700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>27600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>26300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>22900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>20700</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>10</v>
       </c>
@@ -4088,8 +4207,11 @@
       <c r="AC52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,71 +4293,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1580200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1584200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1546700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1563800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1589700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1552100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1533000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1509000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1529500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1467400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1466100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1466300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1480400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1530100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1123500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1115200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1074300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1055300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>909400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>893900</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>10</v>
       </c>
@@ -4254,8 +4379,11 @@
       <c r="AC54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,71 +4445,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E57" s="3">
         <v>22000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>18900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>25900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>21100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1800</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>10</v>
       </c>
@@ -4399,34 +4529,37 @@
       <c r="AC57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E58" s="3">
         <v>5200</v>
-      </c>
-      <c r="E58" s="3">
-        <v>4700</v>
       </c>
       <c r="F58" s="3">
         <v>4700</v>
       </c>
       <c r="G58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H58" s="3">
         <v>5800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>6500</v>
       </c>
       <c r="J58" s="3">
         <v>6500</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -4482,71 +4615,74 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>336900</v>
+      </c>
+      <c r="E59" s="3">
         <v>329400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>317600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>313900</v>
       </c>
-      <c r="G59" s="3">
-        <v>320300</v>
-      </c>
       <c r="H59" s="3">
+        <v>321300</v>
+      </c>
+      <c r="I59" s="3">
         <v>312200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>292900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>280500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>345600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>329800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>300300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>280300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>277200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>310400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>219400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>197200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>192600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>174300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>157500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>146300</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>10</v>
       </c>
@@ -4565,71 +4701,74 @@
       <c r="AC59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>421400</v>
+      </c>
+      <c r="E60" s="3">
         <v>419000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>409000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>404000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>422200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>401300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>363600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>342900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>361000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>346700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>309800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>289100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>286500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>323100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>228400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>202900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>199600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>181000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>161400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>148100</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>10</v>
       </c>
@@ -4648,53 +4787,56 @@
       <c r="AC60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>385500</v>
+      </c>
+      <c r="E61" s="3">
         <v>386900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>384500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>384100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>383300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>383500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>384300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>385400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>364500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>363900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>363300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>362600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>362000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>361500</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4705,14 +4847,14 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>201900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>201600</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4731,71 +4873,74 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>100</v>
+      </c>
+      <c r="E62" s="3">
         <v>400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>7200</v>
       </c>
       <c r="J62" s="3">
         <v>7200</v>
       </c>
       <c r="K62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="L62" s="3">
         <v>102700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>97100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>99000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>92600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>93400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>98800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>91100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>93000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>63700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>58900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>49200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>47800</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>10</v>
       </c>
@@ -4814,8 +4959,11 @@
       <c r="AC62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,71 +5217,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>864200</v>
+      </c>
+      <c r="E66" s="3">
         <v>863700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>854500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>847700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>872100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>852600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>824700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>803500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>828200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>807700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>772100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>744400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>742000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>783300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>319600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>295900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>263300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>239900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>412500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>397400</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>10</v>
       </c>
@@ -5146,8 +5303,11 @@
       <c r="AC66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,71 +5679,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-522600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-506200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-493900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-439300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-418800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-401400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-369100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-332900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-308700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-287500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-256200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-193000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-167400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-143700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-113300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-90800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-92200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-78800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-73700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-73300</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>10</v>
       </c>
@@ -5592,8 +5765,11 @@
       <c r="AC72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,71 +6023,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>716000</v>
+      </c>
+      <c r="E76" s="3">
         <v>720500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>692300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>716100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>717500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>699400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>708400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>705500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>701300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>659800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>693900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>721900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>738400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>746800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>804000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>819300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>811000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>815400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>496800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>496500</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>10</v>
       </c>
@@ -5924,8 +6109,11 @@
       <c r="AC76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-20500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-32300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-36200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-24200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-21200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-63100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-23800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-11200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,13 +6406,14 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="E83" s="3">
         <v>1900</v>
@@ -6224,10 +6422,10 @@
         <v>1900</v>
       </c>
       <c r="G83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H83" s="3">
         <v>1800</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1600</v>
       </c>
       <c r="I83" s="3">
         <v>1600</v>
@@ -6236,44 +6434,44 @@
         <v>1600</v>
       </c>
       <c r="K83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L83" s="3">
         <v>13100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>13900</v>
       </c>
       <c r="N83" s="3">
         <v>13900</v>
       </c>
       <c r="O83" s="3">
+        <v>13900</v>
+      </c>
+      <c r="P83" s="3">
         <v>13800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13700</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>9800</v>
       </c>
       <c r="R83" s="3">
         <v>9800</v>
       </c>
       <c r="S83" s="3">
+        <v>9800</v>
+      </c>
+      <c r="T83" s="3">
         <v>10100</v>
-      </c>
-      <c r="T83" s="3">
-        <v>9400</v>
       </c>
       <c r="U83" s="3">
         <v>9400</v>
       </c>
       <c r="V83" s="3">
+        <v>9400</v>
+      </c>
+      <c r="W83" s="3">
         <v>9600</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>10</v>
       </c>
@@ -6292,8 +6490,11 @@
       <c r="AC83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,71 +6920,74 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E89" s="3">
         <v>23100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>14300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-15900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>33300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-24800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>27200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>46500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>19300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>26800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>34000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>19800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>23600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>18300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-8800</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>10</v>
       </c>
@@ -6790,8 +7006,11 @@
       <c r="AC89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,71 +7040,72 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-700</v>
       </c>
       <c r="I91" s="3">
         <v>-700</v>
       </c>
       <c r="J91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1000</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>10</v>
       </c>
@@ -6904,8 +7124,11 @@
       <c r="AC91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,71 +7296,74 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-21900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-351700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1000</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>10</v>
       </c>
@@ -7153,8 +7382,11 @@
       <c r="AC94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7210,8 +7443,8 @@
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7267,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,71 +7758,74 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-39200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2700</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-23400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>326800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>115900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>10</v>
       </c>
@@ -7599,59 +7844,62 @@
       <c r="AC100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-100</v>
       </c>
       <c r="O101" s="3">
         <v>-100</v>
       </c>
       <c r="P101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-400</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>10</v>
       </c>
@@ -7667,8 +7915,8 @@
       <c r="X101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -7682,71 +7930,74 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E102" s="3">
         <v>17600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-27300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-19000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>16000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>16100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-24100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>43100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>17800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-50600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>30300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>17500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>139000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>15700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9800</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>10</v>
       </c>
@@ -7763,6 +8014,9 @@
         <v>10</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JAMF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JAMF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>JAMF</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>167600</v>
+      </c>
+      <c r="E8" s="3">
         <v>163000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>159300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>153000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>152100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>150600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>142600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>135100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>132200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>130300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>124600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>115600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>108300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>103800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>95600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>86200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>80700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>76100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>70400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>62200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>60400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>57000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>54600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>48300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>44100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>41900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>39300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E9" s="3">
         <v>32100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>32800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>31600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>31500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>29600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>28600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>27500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>26400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>30400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>31200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>29400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>28200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>27200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>17300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>17100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>13600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>15000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13000</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>12600</v>
       </c>
       <c r="AC9" s="3">
         <v>12600</v>
       </c>
       <c r="AD9" s="3">
+        <v>12600</v>
+      </c>
+      <c r="AE9" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>133600</v>
+      </c>
+      <c r="E10" s="3">
         <v>130800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>126400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>121400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>120600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>121100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>114000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>107600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>105800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>99900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>93400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>86200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>80100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>76600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>69100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>66900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>63400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>59000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>55200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>48600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>45400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>41600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>40500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>34800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>31100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>29300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>26700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E12" s="3">
         <v>33800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>35700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>34500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>33000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>32500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>34200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>34400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>32000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>30100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>33300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>24200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>23300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>16900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>15300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>14900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>11700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>13400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>9500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>8800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>8400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1242,94 +1259,100 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E14" s="3">
         <v>900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>9300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>10400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>6900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-2100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1600</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB14" s="3">
         <v>900</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1337,34 +1360,34 @@
         <v>9700</v>
       </c>
       <c r="E15" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F15" s="3">
         <v>10000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10200</v>
-      </c>
-      <c r="H15" s="3">
-        <v>10900</v>
       </c>
       <c r="I15" s="3">
         <v>10900</v>
       </c>
       <c r="J15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K15" s="3">
         <v>10600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>10500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8400</v>
-      </c>
-      <c r="N15" s="3">
-        <v>8300</v>
       </c>
       <c r="O15" s="3">
         <v>8300</v>
@@ -1373,40 +1396,40 @@
         <v>8300</v>
       </c>
       <c r="Q15" s="3">
+        <v>8300</v>
+      </c>
+      <c r="R15" s="3">
         <v>8200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>6600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>6700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>7100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>6400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>6500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>6600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>5500</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>5600</v>
       </c>
       <c r="Z15" s="3">
         <v>5600</v>
       </c>
       <c r="AA15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AB15" s="3">
         <v>6300</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>5400</v>
       </c>
       <c r="AC15" s="3">
         <v>5400</v>
@@ -1414,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>5400</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>169200</v>
+      </c>
+      <c r="E17" s="3">
         <v>174300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>174000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>169600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>163900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>164900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>171600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>172000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>156900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>155000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>153200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>177500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>132000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>129900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>125900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>102300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>84900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>90900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>76000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>58000</v>
-      </c>
-      <c r="W17" s="3">
-        <v>66900</v>
       </c>
       <c r="X17" s="3">
         <v>66900</v>
       </c>
       <c r="Y17" s="3">
+        <v>66900</v>
+      </c>
+      <c r="Z17" s="3">
         <v>54400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>52700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>50300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>48600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>44300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-14700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-14200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-28900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-36900</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-24700</v>
       </c>
       <c r="L18" s="3">
         <v>-24700</v>
       </c>
       <c r="M18" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="N18" s="3">
         <v>-28600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-61900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-23700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-26100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-30300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-16100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-14800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-6200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,58 +1680,59 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E20" s="3">
         <v>5700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-200</v>
       </c>
       <c r="T20" s="3">
         <v>-200</v>
@@ -1707,141 +1741,147 @@
         <v>-200</v>
       </c>
       <c r="V20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-7300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-20700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-25300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-13600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-9400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-48600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-10600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-16900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>13700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2900</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB21" s="3">
         <v>2600</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3">
         <v>3800</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="F22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22" s="3">
         <v>3600</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>10</v>
       </c>
@@ -1854,41 +1894,41 @@
       <c r="M22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O22" s="3">
         <v>600</v>
-      </c>
-      <c r="O22" s="3">
-        <v>900</v>
       </c>
       <c r="P22" s="3">
         <v>900</v>
       </c>
       <c r="Q22" s="3">
+        <v>900</v>
+      </c>
+      <c r="R22" s="3">
         <v>1400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>200</v>
-      </c>
-      <c r="S22" s="3">
-        <v>100</v>
       </c>
       <c r="T22" s="3">
         <v>100</v>
       </c>
       <c r="U22" s="3">
+        <v>100</v>
+      </c>
+      <c r="V22" s="3">
         <v>1200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>5500</v>
       </c>
       <c r="Z22" s="3">
         <v>5500</v>
@@ -1897,188 +1937,197 @@
         <v>5500</v>
       </c>
       <c r="AB22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AC22" s="3">
         <v>4300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>4700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-19500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-16300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-32800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-35100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-23600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-22500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-31200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-63200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-25400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-32000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-15100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-7000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-14800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-12900</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1900</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-3200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-20500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-32300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-36200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-24200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-21200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-31300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-63100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-25600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-23800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-16500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-20500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-32300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-36200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-24200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-21200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-63100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-25600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-23800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-30400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-16500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,58 +2746,61 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
-      </c>
-      <c r="S32" s="3">
-        <v>200</v>
       </c>
       <c r="T32" s="3">
         <v>200</v>
@@ -2739,120 +2809,126 @@
         <v>200</v>
       </c>
       <c r="V32" s="3">
+        <v>200</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-20500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-32300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-36200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-24200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-21200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-63100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-25600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-23800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-30400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-16500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-10300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-20500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-32300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-36200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-24200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-21200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-63100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-25600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-23800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-30400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-16500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-10300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,74 +3264,75 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>222400</v>
+      </c>
+      <c r="E41" s="3">
         <v>224700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>218400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>224500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>243600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>227600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>211500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>200300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>224300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>225500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>182300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>164600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>177200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>227100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>226500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>196200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>194900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>177500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>38400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>22700</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>10</v>
       </c>
@@ -3264,8 +3351,11 @@
       <c r="AD41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3350,74 +3440,77 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>138400</v>
+      </c>
+      <c r="E43" s="3">
         <v>138800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>114000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>109100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>95500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>108200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>92400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>101000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>85800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>88600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>93300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>96900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>81400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>79800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>70100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>67200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>76500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>69700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>64800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>53800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>46700</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>10</v>
       </c>
@@ -3436,8 +3529,11 @@
       <c r="AD43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3465,8 +3561,8 @@
       <c r="K44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3522,74 +3618,77 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E45" s="3">
         <v>44800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>43800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>41900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>38200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>32900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>28800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>28400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>24400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>37900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>34700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>33900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>27600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>28500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>22700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>25900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>24500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>25000</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>10</v>
       </c>
@@ -3608,74 +3707,77 @@
       <c r="AD45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>431600</v>
+      </c>
+      <c r="E46" s="3">
         <v>424700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>398700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>374000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>386700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>402600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>372000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>359000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>333800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>351000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>357700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>317200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>284100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>291600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>331200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>321300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>301200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>287200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>268100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>116700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>94400</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>10</v>
       </c>
@@ -3694,13 +3796,16 @@
       <c r="AD46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>10</v>
+      <c r="D47" s="3">
+        <v>8500</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>10</v>
@@ -3720,12 +3825,12 @@
       <c r="J47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L47" s="3">
         <v>2000</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -3780,74 +3885,77 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E48" s="3">
         <v>36300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>36900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>36500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>38900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>43200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>43600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>44400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>46800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>38300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12300</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>10</v>
       </c>
@@ -3866,74 +3974,77 @@
       <c r="AD48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1030500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1030400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1060600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1053200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1062300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1075000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1073300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1068000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1072300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1075700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1015600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1057200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1093100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1110300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1122800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>730900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>739400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>744400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>749900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>758200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>766600</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>10</v>
       </c>
@@ -3952,8 +4063,11 @@
       <c r="AD49" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,74 +4241,77 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E52" s="3">
         <v>26100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>23200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>27800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>24400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>21300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>20400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>59600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>50600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>47300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>42300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>40200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>58500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>54100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>57700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>27600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>26300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>22900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>20700</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>10</v>
       </c>
@@ -4210,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,74 +4419,77 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1588600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1580200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1584200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1546700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1563800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1589700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1552100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1533000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1509000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1529500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1467400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1466100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1466300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1480400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1530100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1123500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1115200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1074300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1055300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>909400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>893900</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>10</v>
       </c>
@@ -4382,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,74 +4576,75 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E57" s="3">
         <v>18400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>22000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>25900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1800</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>10</v>
       </c>
@@ -4532,37 +4663,40 @@
       <c r="AD57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E58" s="3">
         <v>5100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5200</v>
-      </c>
-      <c r="F58" s="3">
-        <v>4700</v>
       </c>
       <c r="G58" s="3">
         <v>4700</v>
       </c>
       <c r="H58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="I58" s="3">
         <v>5800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>6500</v>
       </c>
       <c r="K58" s="3">
         <v>6500</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4618,74 +4752,77 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>327200</v>
+      </c>
+      <c r="E59" s="3">
         <v>336900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>329400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>317600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>313900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>321300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>312200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>292900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>280500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>345600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>329800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>300300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>280300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>277200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>310400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>219400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>197200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>192600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>174300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>157500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>146300</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>10</v>
       </c>
@@ -4704,74 +4841,77 @@
       <c r="AD59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>399100</v>
+      </c>
+      <c r="E60" s="3">
         <v>421400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>419000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>409000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>404000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>422200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>401300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>363600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>342900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>361000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>346700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>309800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>289100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>286500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>323100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>228400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>202900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>199600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>181000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>161400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>148100</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>10</v>
       </c>
@@ -4790,56 +4930,59 @@
       <c r="AD60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>385100</v>
+      </c>
+      <c r="E61" s="3">
         <v>385500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>386900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>384500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>384100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>383300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>383500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>384300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>385400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>364500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>363900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>363300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>362600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>362000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>361500</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4850,14 +4993,14 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>201900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>201600</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4876,8 +5019,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4885,65 +5031,65 @@
         <v>100</v>
       </c>
       <c r="E62" s="3">
+        <v>100</v>
+      </c>
+      <c r="F62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3600</v>
-      </c>
-      <c r="J62" s="3">
-        <v>7200</v>
       </c>
       <c r="K62" s="3">
         <v>7200</v>
       </c>
       <c r="L62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="M62" s="3">
         <v>102700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>97100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>99000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>92600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>93400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>98800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>91100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>93000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>63700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>58900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>49200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>47800</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>10</v>
       </c>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,74 +5375,77 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>841400</v>
+      </c>
+      <c r="E66" s="3">
         <v>864200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>863700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>854500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>847700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>872100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>852600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>824700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>803500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>828200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>807700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>772100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>744400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>742000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>783300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>319600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>295900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>263300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>239900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>412500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>397400</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>10</v>
       </c>
@@ -5306,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,74 +5853,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-522100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-522600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-506200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-493900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-439300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-418800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-401400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-369100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-332900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-308700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-287500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-256200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-193000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-167400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-143700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-113300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-90800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-92200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-78800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-73700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-73300</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>10</v>
       </c>
@@ -5768,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,74 +6209,77 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>747200</v>
+      </c>
+      <c r="E76" s="3">
         <v>716000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>720500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>692300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>716100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>717500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>699400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>708400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>705500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>701300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>659800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>693900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>721900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>738400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>746800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>804000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>819300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>811000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>815400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>496800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>496500</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>10</v>
       </c>
@@ -6112,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-20500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-32300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-36200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-24200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-21200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-63100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-25600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-23800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-30400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-16500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-10300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6416,7 +6615,7 @@
         <v>1800</v>
       </c>
       <c r="E83" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="F83" s="3">
         <v>1900</v>
@@ -6425,10 +6624,10 @@
         <v>1900</v>
       </c>
       <c r="H83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I83" s="3">
         <v>1800</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1600</v>
       </c>
       <c r="J83" s="3">
         <v>1600</v>
@@ -6437,44 +6636,44 @@
         <v>1600</v>
       </c>
       <c r="L83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M83" s="3">
         <v>13100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>13900</v>
       </c>
       <c r="O83" s="3">
         <v>13900</v>
       </c>
       <c r="P83" s="3">
+        <v>13900</v>
+      </c>
+      <c r="Q83" s="3">
         <v>13800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13700</v>
-      </c>
-      <c r="R83" s="3">
-        <v>9800</v>
       </c>
       <c r="S83" s="3">
         <v>9800</v>
       </c>
       <c r="T83" s="3">
+        <v>9800</v>
+      </c>
+      <c r="U83" s="3">
         <v>10100</v>
-      </c>
-      <c r="U83" s="3">
-        <v>9400</v>
       </c>
       <c r="V83" s="3">
         <v>9400</v>
       </c>
       <c r="W83" s="3">
+        <v>9400</v>
+      </c>
+      <c r="X83" s="3">
         <v>9600</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>10</v>
       </c>
@@ -6493,8 +6692,11 @@
       <c r="AD83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,74 +7137,77 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E89" s="3">
         <v>9700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>23100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-15900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>15900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>33300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-24800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>27200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>46500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>19300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>26800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>34000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>19800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>23600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>18300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-8800</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>10</v>
       </c>
@@ -7009,8 +7226,11 @@
       <c r="AD89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,74 +7261,75 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-700</v>
       </c>
       <c r="J91" s="3">
         <v>-700</v>
       </c>
       <c r="K91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1000</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>10</v>
       </c>
@@ -7127,8 +7348,11 @@
       <c r="AD91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,74 +7526,77 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-21900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-27500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-351700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1000</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>10</v>
       </c>
@@ -7385,8 +7615,11 @@
       <c r="AD94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7446,8 +7680,8 @@
       <c r="K96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,74 +8004,77 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-39200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2700</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>326800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>115900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>10</v>
       </c>
@@ -7847,62 +8093,65 @@
       <c r="AD100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-100</v>
       </c>
       <c r="P101" s="3">
         <v>-100</v>
       </c>
       <c r="Q101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R101" s="3">
         <v>-600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-400</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>10</v>
       </c>
@@ -7918,8 +8167,8 @@
       <c r="Y101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
+      <c r="Z101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
@@ -7933,74 +8182,77 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E102" s="3">
         <v>6300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>17600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-27300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-19000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>16000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>16100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-24100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>43100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>17800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-50600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>30300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>17500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>139000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>15700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-9800</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>10</v>
       </c>
@@ -8017,6 +8269,9 @@
         <v>10</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>10</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JAMF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JAMF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
   <si>
     <t>JAMF</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>176500</v>
+      </c>
+      <c r="E8" s="3">
         <v>167600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>163000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>159300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>153000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>152100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>150600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>142600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>135100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>132200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>130300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>124600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>115600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>108300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>103800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>95600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>86200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>80700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>76100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>70400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>62200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>60400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>57000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>54600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>48300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>44100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>41900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>39300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>34600</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E9" s="3">
         <v>34000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>32100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>32800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>31600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>31500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>29600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>28600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>27500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>30400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>31200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>29400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>28200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>27200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>17300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>17100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>15200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>15000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>15400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>14100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13000</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>12600</v>
       </c>
       <c r="AD9" s="3">
         <v>12600</v>
       </c>
       <c r="AE9" s="3">
+        <v>12600</v>
+      </c>
+      <c r="AF9" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>137600</v>
+      </c>
+      <c r="E10" s="3">
         <v>133600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>130800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>126400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>121400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>120600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>121100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>114000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>107600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>105800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>99900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>93400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>86200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>80100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>76600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>69100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>66900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>63400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>59000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>55200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>48600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>45400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>41600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>40500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>34800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>31100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>29300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>26700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,97 +1097,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E12" s="3">
         <v>34800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>33800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>35700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>34500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>33000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>32500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>34200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>34400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>32000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>30100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>33300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>24200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>23300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>24700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>16900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>15300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>14900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>11700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>12300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>13400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>10900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>8800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>8400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1262,135 +1279,141 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E14" s="3">
         <v>2600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1200</v>
       </c>
-      <c r="G14" s="3">
-        <v>3400</v>
-      </c>
       <c r="H14" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I14" s="3">
         <v>9300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>10400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>6900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-2100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1600</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC14" s="3">
         <v>900</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>9700</v>
+        <v>13000</v>
       </c>
       <c r="E15" s="3">
         <v>9700</v>
       </c>
       <c r="F15" s="3">
+        <v>9700</v>
+      </c>
+      <c r="G15" s="3">
         <v>10000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>10200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>10900</v>
       </c>
       <c r="J15" s="3">
         <v>10900</v>
       </c>
       <c r="K15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="L15" s="3">
         <v>10600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>10500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8400</v>
-      </c>
-      <c r="O15" s="3">
-        <v>8300</v>
       </c>
       <c r="P15" s="3">
         <v>8300</v>
@@ -1399,40 +1422,40 @@
         <v>8300</v>
       </c>
       <c r="R15" s="3">
+        <v>8300</v>
+      </c>
+      <c r="S15" s="3">
         <v>8200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>6600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>6700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>7100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>6400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>6500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>6600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>5500</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>5600</v>
       </c>
       <c r="AA15" s="3">
         <v>5600</v>
       </c>
       <c r="AB15" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AC15" s="3">
         <v>6300</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>5400</v>
       </c>
       <c r="AD15" s="3">
         <v>5400</v>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>5400</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>187400</v>
+      </c>
+      <c r="E17" s="3">
         <v>169200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>174300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>174000</v>
       </c>
-      <c r="G17" s="3">
-        <v>169600</v>
-      </c>
       <c r="H17" s="3">
+        <v>169400</v>
+      </c>
+      <c r="I17" s="3">
         <v>163900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>164900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>171600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>172000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>156900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>155000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>153200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>177500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>132000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>129900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>125900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>102300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>84900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>90900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>76000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>58000</v>
-      </c>
-      <c r="X17" s="3">
-        <v>66900</v>
       </c>
       <c r="Y17" s="3">
         <v>66900</v>
       </c>
       <c r="Z17" s="3">
+        <v>66900</v>
+      </c>
+      <c r="AA17" s="3">
         <v>54400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>52700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>50300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>48600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>44300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-11300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14700</v>
       </c>
-      <c r="G18" s="3">
-        <v>-16500</v>
-      </c>
       <c r="H18" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-11800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-14200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-28900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-36900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-24700</v>
       </c>
       <c r="M18" s="3">
         <v>-24700</v>
       </c>
       <c r="N18" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="O18" s="3">
         <v>-28600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-61900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-26100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-30300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-16100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-14800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-6200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-8000</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,61 +1714,62 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-300</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-200</v>
       </c>
       <c r="U20" s="3">
         <v>-200</v>
@@ -1744,147 +1778,153 @@
         <v>-200</v>
       </c>
       <c r="W20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-200</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E21" s="3">
         <v>11300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-7300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-6000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="I21" s="3">
         <v>-2000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-20700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-25300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-13600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-9400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-17300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-48600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-12300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-16900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>13700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2900</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC21" s="3">
         <v>2600</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="3">
         <v>3800</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22" s="3">
         <v>3600</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>10</v>
       </c>
@@ -1897,41 +1937,41 @@
       <c r="N22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="3">
         <v>600</v>
-      </c>
-      <c r="P22" s="3">
-        <v>900</v>
       </c>
       <c r="Q22" s="3">
         <v>900</v>
       </c>
       <c r="R22" s="3">
+        <v>900</v>
+      </c>
+      <c r="S22" s="3">
         <v>1400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>200</v>
-      </c>
-      <c r="T22" s="3">
-        <v>100</v>
       </c>
       <c r="U22" s="3">
         <v>100</v>
       </c>
       <c r="V22" s="3">
+        <v>100</v>
+      </c>
+      <c r="W22" s="3">
         <v>1200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>5000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>5500</v>
       </c>
       <c r="AA22" s="3">
         <v>5500</v>
@@ -1940,194 +1980,203 @@
         <v>5500</v>
       </c>
       <c r="AC22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AD22" s="3">
         <v>4300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>4700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E23" s="3">
         <v>400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-19500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-32800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-35100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-23600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-22500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-31200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-63200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-25400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-27000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-32000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-15100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-7000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-14800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-10100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-9800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-12900</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-4900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1900</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E26" s="3">
         <v>500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-19300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-32300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-36200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-31300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-63100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-25600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-23800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-30400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-16500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E27" s="3">
         <v>500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-19300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-20500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-32300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-36200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-21200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-63100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-25600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-23800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-30400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-16500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2632,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,61 +2816,64 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
         <v>3200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>300</v>
-      </c>
-      <c r="T32" s="3">
-        <v>200</v>
       </c>
       <c r="U32" s="3">
         <v>200</v>
@@ -2812,123 +2882,129 @@
         <v>200</v>
       </c>
       <c r="W32" s="3">
+        <v>200</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>200</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E33" s="3">
         <v>500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-19300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-20500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-32300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-36200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-21200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-63100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-25600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-23800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-30400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-16500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E35" s="3">
         <v>500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-19300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-20500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-32300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-36200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-21200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-63100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-25600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-23800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-30400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-16500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,77 +3351,78 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>481500</v>
+      </c>
+      <c r="E41" s="3">
         <v>222400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>224700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>218400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>200900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>224500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>243600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>227600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>211500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>200300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>224300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>225500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>182300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>164600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>177200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>227100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>226500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>196200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>194900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>177500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>38400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>22700</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>10</v>
       </c>
@@ -3354,8 +3441,11 @@
       <c r="AE41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,77 +3533,80 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>150300</v>
+      </c>
+      <c r="E43" s="3">
         <v>138400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>138800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>114000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>109100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>95500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>108200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>92400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>101000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>85800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>88600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>93300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>96900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>81400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>79800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>70100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>67200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>76500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>69700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>64800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>53800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>46700</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>10</v>
       </c>
@@ -3532,8 +3625,11 @@
       <c r="AE43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3564,8 +3660,8 @@
       <c r="L44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3621,77 +3717,80 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E45" s="3">
         <v>47500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>44800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>43800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>41900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>38200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>28800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>38900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>37900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>38100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>34700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>33900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>27600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>28500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>22700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>25900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>24500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>25000</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>10</v>
       </c>
@@ -3710,77 +3809,80 @@
       <c r="AE45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>702300</v>
+      </c>
+      <c r="E46" s="3">
         <v>431600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>424700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>398700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>374000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>386700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>402600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>372000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>359000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>333800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>351000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>357700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>317200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>284100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>291600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>331200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>321300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>301200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>287200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>268100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>116700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>94400</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>10</v>
       </c>
@@ -3799,17 +3901,20 @@
       <c r="AE46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E47" s="3">
         <v>8500</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>10</v>
       </c>
@@ -3828,12 +3933,12 @@
       <c r="K47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M47" s="3">
         <v>2000</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -3888,77 +3993,80 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E48" s="3">
         <v>36800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>36300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>36900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>36500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>38900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>41000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>43200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>43600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>44400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>46800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>38300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>17000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>15100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12300</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>10</v>
       </c>
@@ -3977,77 +4085,80 @@
       <c r="AE48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1263400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1030500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1030400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1060600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1053200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1062300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1075000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1073300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1068000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1072300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1075700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1015600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1057200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1093100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1110300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1122800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>730900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>739400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>744400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>749900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>758200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>766600</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>10</v>
       </c>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,77 +4361,80 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E52" s="3">
         <v>20700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>23200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>27800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>24400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>20400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>59600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>50600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>47300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>42300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>40200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>58500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>54100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>57700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>27600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>26300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>22900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>20700</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>10</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,77 +4545,80 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2089900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1588600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1580200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1584200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1546700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1563800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1589700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1552100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1533000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1509000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1529500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1467400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1466100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1466300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1480400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1530100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1123500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1115200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1074300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1055300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>909400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>893900</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>10</v>
       </c>
@@ -4511,8 +4637,11 @@
       <c r="AE54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,77 +4707,78 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E57" s="3">
         <v>20300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>18400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>20400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>25900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1800</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>10</v>
       </c>
@@ -4666,40 +4797,43 @@
       <c r="AE57" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E58" s="3">
         <v>5300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5200</v>
-      </c>
-      <c r="G58" s="3">
-        <v>4700</v>
       </c>
       <c r="H58" s="3">
         <v>4700</v>
       </c>
       <c r="I58" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J58" s="3">
         <v>5800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6200</v>
-      </c>
-      <c r="K58" s="3">
-        <v>6500</v>
       </c>
       <c r="L58" s="3">
         <v>6500</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4755,77 +4889,80 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>354500</v>
+      </c>
+      <c r="E59" s="3">
         <v>327200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>336900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>329400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>317600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>313900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>321300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>312200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>292900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>280500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>345600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>329800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>300300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>280300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>277200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>310400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>219400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>197200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>192600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>174300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>157500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>146300</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>10</v>
       </c>
@@ -4844,77 +4981,80 @@
       <c r="AE59" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>482800</v>
+      </c>
+      <c r="E60" s="3">
         <v>399100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>421400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>419000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>409000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>404000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>422200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>401300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>363600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>342900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>361000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>346700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>309800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>289100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>286500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>323100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>228400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>202900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>199600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>181000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>161400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>148100</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>10</v>
       </c>
@@ -4933,59 +5073,62 @@
       <c r="AE60" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>769700</v>
+      </c>
+      <c r="E61" s="3">
         <v>385100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>385500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>386900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>384500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>384100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>383300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>383500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>384300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>385400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>364500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>363900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>363300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>362600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>362000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>361500</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4996,14 +5139,14 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>201900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>201600</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5022,77 +5165,80 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
         <v>100</v>
       </c>
       <c r="F62" s="3">
+        <v>100</v>
+      </c>
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>7200</v>
       </c>
       <c r="L62" s="3">
         <v>7200</v>
       </c>
       <c r="M62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="N62" s="3">
         <v>102700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>97100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>99000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>92600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>93400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>98800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>91100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>93000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>63700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>58900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>49200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>47800</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>10</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,77 +5533,80 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1314700</v>
+      </c>
+      <c r="E66" s="3">
         <v>841400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>864200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>863700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>854500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>847700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>872100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>852600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>824700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>803500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>828200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>807700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>772100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>744400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>742000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>783300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>319600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>295900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>263300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>239900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>412500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>397400</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>10</v>
       </c>
@@ -5467,8 +5625,11 @@
       <c r="AE66" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,77 +6027,80 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-543000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-522100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-522600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-506200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-493900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-439300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-418800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-401400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-369100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-332900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-308700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-287500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-256200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-193000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-167400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-143700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-113300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-90800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-92200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-78800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-73700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-73300</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>10</v>
       </c>
@@ -5945,8 +6119,11 @@
       <c r="AE72" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,77 +6395,80 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>775200</v>
+      </c>
+      <c r="E76" s="3">
         <v>747200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>716000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>720500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>692300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>716100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>717500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>699400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>708400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>705500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>701300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>659800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>693900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>721900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>738400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>746800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>804000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>819300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>811000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>815400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>496800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>496500</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>10</v>
       </c>
@@ -6301,8 +6487,11 @@
       <c r="AE76" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="E81" s="3">
         <v>500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-19300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-20500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-32300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-36200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-21200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-63100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-25600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-23800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-30400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-16500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,19 +6804,20 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="E83" s="3">
         <v>1800</v>
       </c>
       <c r="F83" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="G83" s="3">
         <v>1900</v>
@@ -6627,10 +6826,10 @@
         <v>1900</v>
       </c>
       <c r="I83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J83" s="3">
         <v>1800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1600</v>
       </c>
       <c r="K83" s="3">
         <v>1600</v>
@@ -6639,44 +6838,44 @@
         <v>1600</v>
       </c>
       <c r="M83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N83" s="3">
         <v>13100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>13900</v>
       </c>
       <c r="P83" s="3">
         <v>13900</v>
       </c>
       <c r="Q83" s="3">
+        <v>13900</v>
+      </c>
+      <c r="R83" s="3">
         <v>13800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13700</v>
-      </c>
-      <c r="S83" s="3">
-        <v>9800</v>
       </c>
       <c r="T83" s="3">
         <v>9800</v>
       </c>
       <c r="U83" s="3">
+        <v>9800</v>
+      </c>
+      <c r="V83" s="3">
         <v>10100</v>
-      </c>
-      <c r="V83" s="3">
-        <v>9400</v>
       </c>
       <c r="W83" s="3">
         <v>9400</v>
       </c>
       <c r="X83" s="3">
+        <v>9400</v>
+      </c>
+      <c r="Y83" s="3">
         <v>9600</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>10</v>
       </c>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,77 +7354,80 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E89" s="3">
         <v>4100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>23100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-15900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>33300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-24800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>27200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>46500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>19300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>26800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>34000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>19800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>23600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>18300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>10</v>
       </c>
@@ -7229,8 +7446,11 @@
       <c r="AE89" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,77 +7482,78 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-700</v>
       </c>
       <c r="K91" s="3">
         <v>-700</v>
       </c>
       <c r="L91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>10</v>
       </c>
@@ -7351,8 +7572,11 @@
       <c r="AE91" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,77 +7756,80 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-176400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-21900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-27500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-351700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>10</v>
       </c>
@@ -7618,8 +7848,11 @@
       <c r="AE94" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7683,8 +7917,8 @@
       <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,77 +8250,80 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>398200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-39200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2700</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>2500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-23400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>326800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>115900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>10</v>
       </c>
@@ -8096,65 +8342,68 @@
       <c r="AE100" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-600</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-100</v>
       </c>
       <c r="Q101" s="3">
         <v>-100</v>
       </c>
       <c r="R101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S101" s="3">
         <v>-600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-400</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>10</v>
       </c>
@@ -8170,8 +8419,8 @@
       <c r="Z101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -8185,77 +8434,80 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>259300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>17600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-19000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>16000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>16100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-24100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>43100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-50600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>30300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>17500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>139000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>15700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>10</v>
       </c>
@@ -8272,6 +8524,9 @@
         <v>10</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>10</v>
       </c>
     </row>
